--- a/artfynd/A 8898-2020 artfynd.xlsx
+++ b/artfynd/A 8898-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8898-2020 artfynd.xlsx
+++ b/artfynd/A 8898-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74500072</v>
+        <v>74770407</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
+        <v>96367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5G8f 3619. SOM: Huperzia selago. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 5G8f 3619. SOM: Platanthera bifolia. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,127 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>74770407</v>
-      </c>
-      <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>219874</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nattviol</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Gräsgölebäcken, Sm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>575565.4608215011</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6342350.5811757</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1988-07-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1988-07-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5G8f 3619. SOM: Platanthera bifolia. LEG: Åke Rühling</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
